--- a/artfynd/A 15267-2025 artfynd.xlsx
+++ b/artfynd/A 15267-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>123452304</v>
       </c>
       <c r="B2" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>123452305</v>
       </c>
       <c r="B3" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -894,6 +894,368 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123747420</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57487</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kopotten, Granbergsdal, N Kga, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>477244</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6585248</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringbarkad tall som dött. Flerskiktat-diameterspritt-olikåldrigt-döda träd. Lämplig trivselmiljö.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123746597</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56697</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kopotten, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>477265</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6585230</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123746816</v>
+      </c>
+      <c r="B6" t="n">
+        <v>90948</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kopotten, Kopotten, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>477268</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6585251</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15267-2025 artfynd.xlsx
+++ b/artfynd/A 15267-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1257,6 +1257,118 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123747933</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97360</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221940</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mellanlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium zeilleri</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Rouy) Greuter &amp; Burdet</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kopotten, Kopotten, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>477110</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6585275</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 15267-2025 artfynd.xlsx
+++ b/artfynd/A 15267-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123452304</v>
+        <v>123452305</v>
       </c>
       <c r="B2" t="n">
-        <v>57487</v>
+        <v>78786</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477270</v>
+        <v>477307</v>
       </c>
       <c r="R2" t="n">
-        <v>6585190</v>
+        <v>6585246</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123452305</v>
+        <v>123452304</v>
       </c>
       <c r="B3" t="n">
-        <v>78781</v>
+        <v>57490</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477307</v>
+        <v>477270</v>
       </c>
       <c r="R3" t="n">
-        <v>6585246</v>
+        <v>6585190</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>123747420</v>
       </c>
       <c r="B4" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123746597</v>
+        <v>123746816</v>
       </c>
       <c r="B5" t="n">
-        <v>56697</v>
+        <v>90953</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,46 +1039,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kopotten, Vrm</t>
+          <t>Kopotten, Kopotten, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477265</v>
+        <v>477268</v>
       </c>
       <c r="R5" t="n">
-        <v>6585230</v>
+        <v>6585251</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1108,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123746816</v>
+        <v>123746597</v>
       </c>
       <c r="B6" t="n">
-        <v>90948</v>
+        <v>56700</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,34 +1151,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kopotten, Kopotten, Vrm</t>
+          <t>Kopotten, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477268</v>
+        <v>477265</v>
       </c>
       <c r="R6" t="n">
-        <v>6585251</v>
+        <v>6585230</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,118 +1256,6 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>123747933</v>
-      </c>
-      <c r="B7" t="n">
-        <v>97360</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>221940</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Mellanlummer</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Lycopodium zeilleri</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Rouy) Greuter &amp; Burdet</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Kopotten, Kopotten, Vrm</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>477110</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6585275</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Karlskoga</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Karlskoga</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Jim Hellquist</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Jim Hellquist</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15267-2025 artfynd.xlsx
+++ b/artfynd/A 15267-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123452305</v>
+        <v>123452304</v>
       </c>
       <c r="B2" t="n">
-        <v>78786</v>
+        <v>57491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477307</v>
+        <v>477270</v>
       </c>
       <c r="R2" t="n">
-        <v>6585246</v>
+        <v>6585190</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123452304</v>
+        <v>123452305</v>
       </c>
       <c r="B3" t="n">
-        <v>57490</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477270</v>
+        <v>477307</v>
       </c>
       <c r="R3" t="n">
-        <v>6585190</v>
+        <v>6585246</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123747420</v>
+        <v>123746816</v>
       </c>
       <c r="B4" t="n">
-        <v>57490</v>
+        <v>90955</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,47 +909,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kopotten, Granbergsdal, N Kga, Vrm</t>
+          <t>Kopotten, Kopotten, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477244</v>
+        <v>477268</v>
       </c>
       <c r="R4" t="n">
-        <v>6585248</v>
+        <v>6585251</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +972,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,12 +982,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringbarkad tall som dött. Flerskiktat-diameterspritt-olikåldrigt-döda träd. Lämplig trivselmiljö.</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123746816</v>
+        <v>123746597</v>
       </c>
       <c r="B5" t="n">
-        <v>90953</v>
+        <v>56700</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,34 +1025,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kopotten, Kopotten, Vrm</t>
+          <t>Kopotten, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477268</v>
+        <v>477265</v>
       </c>
       <c r="R5" t="n">
-        <v>6585251</v>
+        <v>6585230</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123746597</v>
+        <v>123747420</v>
       </c>
       <c r="B6" t="n">
-        <v>56700</v>
+        <v>57491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,25 +1145,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1173,24 +1171,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kopotten, Vrm</t>
+          <t>Kopotten, Granbergsdal, N Kga, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477265</v>
+        <v>477244</v>
       </c>
       <c r="R6" t="n">
-        <v>6585230</v>
+        <v>6585248</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,7 +1227,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringbarkad tall som dött. Flerskiktat-diameterspritt-olikåldrigt-döda träd. Lämplig trivselmiljö.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 15267-2025 artfynd.xlsx
+++ b/artfynd/A 15267-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123452304</v>
+        <v>123452305</v>
       </c>
       <c r="B2" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477270</v>
+        <v>477307</v>
       </c>
       <c r="R2" t="n">
-        <v>6585190</v>
+        <v>6585246</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123452305</v>
+        <v>123452304</v>
       </c>
       <c r="B3" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477307</v>
+        <v>477270</v>
       </c>
       <c r="R3" t="n">
-        <v>6585246</v>
+        <v>6585190</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123746816</v>
+        <v>123746597</v>
       </c>
       <c r="B4" t="n">
-        <v>90955</v>
+        <v>56700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,34 +913,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kopotten, Kopotten, Vrm</t>
+          <t>Kopotten, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477268</v>
+        <v>477265</v>
       </c>
       <c r="R4" t="n">
-        <v>6585251</v>
+        <v>6585230</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -982,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123746597</v>
+        <v>123747420</v>
       </c>
       <c r="B5" t="n">
-        <v>56700</v>
+        <v>57491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,25 +1033,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1047,24 +1059,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kopotten, Vrm</t>
+          <t>Kopotten, Granbergsdal, N Kga, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477265</v>
+        <v>477244</v>
       </c>
       <c r="R5" t="n">
-        <v>6585230</v>
+        <v>6585248</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1115,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringbarkad tall som dött. Flerskiktat-diameterspritt-olikåldrigt-döda träd. Lämplig trivselmiljö.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123747420</v>
+        <v>123746816</v>
       </c>
       <c r="B6" t="n">
-        <v>57491</v>
+        <v>90955</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,47 +1159,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kopotten, Granbergsdal, N Kga, Vrm</t>
+          <t>Kopotten, Kopotten, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477244</v>
+        <v>477268</v>
       </c>
       <c r="R6" t="n">
-        <v>6585248</v>
+        <v>6585251</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,12 +1232,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringbarkad tall som dött. Flerskiktat-diameterspritt-olikåldrigt-döda träd. Lämplig trivselmiljö.</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 15267-2025 artfynd.xlsx
+++ b/artfynd/A 15267-2025 artfynd.xlsx
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123746597</v>
+        <v>123746816</v>
       </c>
       <c r="B4" t="n">
-        <v>56700</v>
+        <v>90955</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,46 +913,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kopotten, Vrm</t>
+          <t>Kopotten, Kopotten, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477265</v>
+        <v>477268</v>
       </c>
       <c r="R4" t="n">
-        <v>6585230</v>
+        <v>6585251</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +972,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +982,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123747420</v>
+        <v>123746597</v>
       </c>
       <c r="B5" t="n">
-        <v>57491</v>
+        <v>56700</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,25 +1021,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1059,21 +1047,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kopotten, Granbergsdal, N Kga, Vrm</t>
+          <t>Kopotten, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477244</v>
+        <v>477265</v>
       </c>
       <c r="R5" t="n">
-        <v>6585248</v>
+        <v>6585230</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,12 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringbarkad tall som dött. Flerskiktat-diameterspritt-olikåldrigt-döda träd. Lämplig trivselmiljö.</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123746816</v>
+        <v>123747420</v>
       </c>
       <c r="B6" t="n">
-        <v>90955</v>
+        <v>57491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,38 +1145,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kopotten, Kopotten, Vrm</t>
+          <t>Kopotten, Granbergsdal, N Kga, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477268</v>
+        <v>477244</v>
       </c>
       <c r="R6" t="n">
-        <v>6585251</v>
+        <v>6585248</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,7 +1227,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringbarkad tall som dött. Flerskiktat-diameterspritt-olikåldrigt-döda träd. Lämplig trivselmiljö.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 15267-2025 artfynd.xlsx
+++ b/artfynd/A 15267-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123452305</v>
+        <v>123452304</v>
       </c>
       <c r="B2" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477307</v>
+        <v>477270</v>
       </c>
       <c r="R2" t="n">
-        <v>6585246</v>
+        <v>6585190</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123452304</v>
+        <v>123452305</v>
       </c>
       <c r="B3" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477270</v>
+        <v>477307</v>
       </c>
       <c r="R3" t="n">
-        <v>6585190</v>
+        <v>6585246</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123746816</v>
+        <v>123746597</v>
       </c>
       <c r="B4" t="n">
-        <v>90955</v>
+        <v>56700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,34 +913,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kopotten, Kopotten, Vrm</t>
+          <t>Kopotten, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477268</v>
+        <v>477265</v>
       </c>
       <c r="R4" t="n">
-        <v>6585251</v>
+        <v>6585230</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -982,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123746597</v>
+        <v>123746816</v>
       </c>
       <c r="B5" t="n">
-        <v>56700</v>
+        <v>90955</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,46 +1037,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kopotten, Vrm</t>
+          <t>Kopotten, Kopotten, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477265</v>
+        <v>477268</v>
       </c>
       <c r="R5" t="n">
-        <v>6585230</v>
+        <v>6585251</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1257,6 +1257,123 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123747933</v>
+      </c>
+      <c r="B7" t="n">
+        <v>96967</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221940</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mellanlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium zeilleri</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Rouy) Greuter &amp; Burdet</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kopotten, Kopotten, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>477110</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6585275</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 15267-2025 artfynd.xlsx
+++ b/artfynd/A 15267-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123452304</v>
+        <v>123452305</v>
       </c>
       <c r="B2" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477270</v>
+        <v>477307</v>
       </c>
       <c r="R2" t="n">
-        <v>6585190</v>
+        <v>6585246</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123452305</v>
+        <v>123452304</v>
       </c>
       <c r="B3" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477307</v>
+        <v>477270</v>
       </c>
       <c r="R3" t="n">
-        <v>6585246</v>
+        <v>6585190</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123746597</v>
+        <v>123746816</v>
       </c>
       <c r="B4" t="n">
-        <v>56700</v>
+        <v>90955</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,46 +913,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kopotten, Vrm</t>
+          <t>Kopotten, Kopotten, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477265</v>
+        <v>477268</v>
       </c>
       <c r="R4" t="n">
-        <v>6585230</v>
+        <v>6585251</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +972,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +982,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123746816</v>
+        <v>123746597</v>
       </c>
       <c r="B5" t="n">
-        <v>90955</v>
+        <v>56700</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,34 +1025,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kopotten, Kopotten, Vrm</t>
+          <t>Kopotten, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477268</v>
+        <v>477265</v>
       </c>
       <c r="R5" t="n">
-        <v>6585251</v>
+        <v>6585230</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 15267-2025 artfynd.xlsx
+++ b/artfynd/A 15267-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1257,6 +1257,123 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123747933</v>
+      </c>
+      <c r="B7" t="n">
+        <v>96989</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221940</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mellanlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium zeilleri</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Rouy) Greuter &amp; Burdet</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kopotten, Kopotten, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>477110</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6585275</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 15267-2025 artfynd.xlsx
+++ b/artfynd/A 15267-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1257,123 +1257,6 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>123747933</v>
-      </c>
-      <c r="B7" t="n">
-        <v>96989</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>221940</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Mellanlummer</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Lycopodium zeilleri</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Rouy) Greuter &amp; Burdet</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Kopotten, Kopotten, Vrm</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>477110</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6585275</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Karlskoga</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Karlskoga</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Jim Hellquist</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Jim Hellquist</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 15267-2025 artfynd.xlsx
+++ b/artfynd/A 15267-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1257,6 +1257,123 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123747933</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97153</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kopotten, Kopotten, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>477110</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6585275</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 15267-2025 artfynd.xlsx
+++ b/artfynd/A 15267-2025 artfynd.xlsx
@@ -1262,12 +1262,7 @@
         <v>123747933</v>
       </c>
       <c r="B7" t="n">
-        <v>97153</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 15267-2025 artfynd.xlsx
+++ b/artfynd/A 15267-2025 artfynd.xlsx
@@ -1262,7 +1262,7 @@
         <v>123747933</v>
       </c>
       <c r="B7" t="n">
-        <v>97208</v>
+        <v>97215</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 15267-2025 artfynd.xlsx
+++ b/artfynd/A 15267-2025 artfynd.xlsx
@@ -1262,7 +1262,7 @@
         <v>123747933</v>
       </c>
       <c r="B7" t="n">
-        <v>97215</v>
+        <v>97218</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 15267-2025 artfynd.xlsx
+++ b/artfynd/A 15267-2025 artfynd.xlsx
@@ -1262,7 +1262,7 @@
         <v>123747933</v>
       </c>
       <c r="B7" t="n">
-        <v>97218</v>
+        <v>97222</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 15267-2025 artfynd.xlsx
+++ b/artfynd/A 15267-2025 artfynd.xlsx
@@ -1262,7 +1262,7 @@
         <v>123747933</v>
       </c>
       <c r="B7" t="n">
-        <v>97222</v>
+        <v>97223</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 15267-2025 artfynd.xlsx
+++ b/artfynd/A 15267-2025 artfynd.xlsx
@@ -1262,7 +1262,7 @@
         <v>123747933</v>
       </c>
       <c r="B7" t="n">
-        <v>97223</v>
+        <v>97225</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 15267-2025 artfynd.xlsx
+++ b/artfynd/A 15267-2025 artfynd.xlsx
@@ -1262,7 +1262,7 @@
         <v>123747933</v>
       </c>
       <c r="B7" t="n">
-        <v>97225</v>
+        <v>97227</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 15267-2025 artfynd.xlsx
+++ b/artfynd/A 15267-2025 artfynd.xlsx
@@ -1262,7 +1262,7 @@
         <v>123747933</v>
       </c>
       <c r="B7" t="n">
-        <v>97227</v>
+        <v>97229</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
